--- a/spectral_centroid/DS-1W複合音和音.xlsx
+++ b/spectral_centroid/DS-1W複合音和音.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Research\recording_application\spectral_centroid\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AFCCED6-F4A0-45AB-8EDA-0F8A035F5C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D000FDD5-9DBB-4EED-A96B-A166C9C62BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -500,61 +500,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US"/>
-                  <a:t>スペクトル重心</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="ja-JP"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -950,61 +895,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="ja-JP" altLang="en-US"/>
-                  <a:t>スペクトル重心</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="ja-JP"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
